--- a/Accounts 2026/Shareholders 2026/01 Shareholders/01 COCO COHEN2026.xlsx
+++ b/Accounts 2026/Shareholders 2026/01 Shareholders/01 COCO COHEN2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrisa\Dropbox\Andrisa\Landco\Accounts 2026\Shareholders 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\landco\Accounts 2026\Shareholders 2026\01 Shareholders\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14474B77-8EBB-4A05-9940-C75E2526996F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3CE52B-4416-4B69-A19C-4AA8B0F2E3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMMERY " sheetId="6" r:id="rId1"/>
@@ -1267,7 +1267,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="INCOME"/>
@@ -1277,23 +1276,39 @@
       <sheetName val="MONTHLY FOR THE YEAR"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0">
+        <row r="51">
+          <cell r="D51">
+            <v>812375</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1">
+        <row r="4">
+          <cell r="C4">
+            <v>-456526.24425000005</v>
+          </cell>
+        </row>
         <row r="7">
           <cell r="C7">
             <v>345627.78249999997</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
       <sheetData sheetId="3">
+        <row r="6">
+          <cell r="D6">
+            <v>38090</v>
+          </cell>
+        </row>
         <row r="7">
           <cell r="D7">
             <v>44850</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
